--- a/youzi/江东猛龙/index.xlsx
+++ b/youzi/江东猛龙/index.xlsx
@@ -39,6 +39,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB0212E"/>
         <bgColor/>
       </patternFill>
@@ -75,7 +123,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,31 +171,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,25 +225,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,43 +261,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC62B3A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,85 +375,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,31 +411,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE35E6A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,79 +435,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,6 +459,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -466,24 +484,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002361</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -766.84万</v>
       </c>
       <c r="E2">
@@ -1836,37 +1836,37 @@
       <c r="I2" s="8">
         <v>10.22</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="2">
         <v>8.42</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="9">
         <v>9.14</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="3">
         <v>14.52</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="11">
         <v>25.99</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="4">
         <v>25.27</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="5">
         <v>22.58</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="6">
         <v>21.15</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="10">
         <v>25.09</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="12">
         <v>28.49</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="13">
         <v>21.86</v>
       </c>
-      <c r="T2" s="12">
+      <c r="T2" s="7">
         <v>236.02</v>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002361</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -845.97万</v>
       </c>
       <c r="E3">
@@ -1895,22 +1895,22 @@
       <c r="H3">
         <v>0.31</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="15">
         <v>9.67</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="16">
         <v>9.05</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="19">
         <v>6.71</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="17">
         <v>5.46</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="23">
         <v>8.89</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="24">
         <v>11.86</v>
       </c>
       <c r="O3" s="25">
@@ -1922,10 +1922,10 @@
       <c r="Q3" s="26">
         <v>0.47</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="20">
         <v>0.62</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="21">
         <v>10.76</v>
       </c>
       <c r="T3" s="14">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300497</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="31" t="str">
         <v>净卖: -2195.55万</v>
       </c>
       <c r="E4">
@@ -1957,40 +1957,40 @@
       <c r="H4">
         <v>16.67</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="39">
         <v>2.88</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="35">
         <v>10.88</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="36">
         <v>24.34</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="32">
         <v>5.76</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="37">
         <v>6.7</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="38">
         <v>7</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="33">
         <v>-8.29</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="27">
         <v>-5.41</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="28">
         <v>-3.59</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="29">
         <v>-7.94</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="30">
         <v>-4.35</v>
       </c>
-      <c r="T4" s="37">
+      <c r="T4" s="34">
         <v>10.76</v>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>603216</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="49" t="str">
         <v>净买: 2090.40万</v>
       </c>
       <c r="E5">
@@ -2019,37 +2019,37 @@
       <c r="H5">
         <v>10</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="41">
         <v>0</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="42">
         <v>10</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="50">
         <v>21</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="43">
         <v>13.35</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="51">
         <v>24.64</v>
       </c>
       <c r="N5" s="47">
         <v>37.13</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="48">
         <v>46.41</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="44">
         <v>61.05</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="52">
         <v>44.93</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="45">
         <v>36.41</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="40">
         <v>47.18</v>
       </c>
       <c r="T5" s="46">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000949</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="56" t="str">
         <v>净卖: -2847.45万</v>
       </c>
       <c r="E6">
@@ -2081,31 +2081,31 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="57">
         <v>10.03</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="58">
         <v>12.24</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="65">
         <v>10.62</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="60">
         <v>6.93</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="63">
         <v>3.98</v>
       </c>
       <c r="N6" s="59">
         <v>4.87</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="53">
         <v>10.62</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="64">
         <v>11.5</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="54">
         <v>7.23</v>
       </c>
       <c r="R6" s="61">
@@ -2114,7 +2114,7 @@
       <c r="S6" s="62">
         <v>0</v>
       </c>
-      <c r="T6" s="53">
+      <c r="T6" s="55">
         <v>7.82</v>
       </c>
     </row>
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="68">
+      <c r="I8" s="70">
         <v>80</v>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="71">
         <v>100</v>
       </c>
-      <c r="K8" s="77">
+      <c r="K8" s="74">
         <v>100</v>
       </c>
-      <c r="L8" s="72">
+      <c r="L8" s="75">
         <v>100</v>
       </c>
-      <c r="M8" s="66">
+      <c r="M8" s="67">
         <v>100</v>
       </c>
-      <c r="N8" s="73">
+      <c r="N8" s="76">
         <v>100</v>
       </c>
-      <c r="O8" s="74">
+      <c r="O8" s="77">
         <v>80</v>
       </c>
-      <c r="P8" s="69">
+      <c r="P8" s="66">
         <v>60</v>
       </c>
-      <c r="Q8" s="70">
+      <c r="Q8" s="68">
         <v>80</v>
       </c>
-      <c r="R8" s="75">
+      <c r="R8" s="72">
         <v>60</v>
       </c>
-      <c r="S8" s="67">
+      <c r="S8" s="69">
         <v>60</v>
       </c>
-      <c r="T8" s="71">
+      <c r="T8" s="73">
         <v>100</v>
       </c>
     </row>
@@ -2225,22 +2225,22 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="82">
+      <c r="I9" s="79">
         <v>6.56</v>
       </c>
-      <c r="J9" s="78">
+      <c r="J9" s="81">
         <v>10.12</v>
       </c>
-      <c r="K9" s="83">
+      <c r="K9" s="87">
         <v>14.36</v>
       </c>
-      <c r="L9" s="87">
+      <c r="L9" s="83">
         <v>9.2</v>
       </c>
-      <c r="M9" s="79">
+      <c r="M9" s="84">
         <v>14.04</v>
       </c>
-      <c r="N9" s="84">
+      <c r="N9" s="82">
         <v>17.23</v>
       </c>
       <c r="O9" s="85">
@@ -2252,13 +2252,13 @@
       <c r="Q9" s="89">
         <v>14.83</v>
       </c>
-      <c r="R9" s="86">
+      <c r="R9" s="80">
         <v>10.81</v>
       </c>
-      <c r="S9" s="80">
+      <c r="S9" s="86">
         <v>15.09</v>
       </c>
-      <c r="T9" s="81">
+      <c r="T9" s="78">
         <v>98.42</v>
       </c>
     </row>

--- a/youzi/江东猛龙/index.xlsx
+++ b/youzi/江东猛龙/index.xlsx
@@ -39,12 +39,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB72432"/>
         <bgColor/>
       </patternFill>
@@ -63,30 +87,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB0212E"/>
         <bgColor/>
       </patternFill>
@@ -117,6 +117,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -135,6 +177,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD73242"/>
         <bgColor/>
       </patternFill>
@@ -147,19 +195,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC92C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,133 +369,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -345,90 +465,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -447,55 +483,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002361</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -766.84万</v>
       </c>
       <c r="E2">
@@ -1833,40 +1833,40 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="5">
         <v>10.22</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="6">
         <v>8.42</v>
       </c>
       <c r="K2" s="9">
         <v>9.14</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="10">
         <v>14.52</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="13">
         <v>25.99</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="1">
         <v>25.27</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="2">
         <v>22.58</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="11">
         <v>21.15</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="3">
         <v>25.09</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="7">
         <v>28.49</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="8">
         <v>21.86</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="12">
         <v>236.02</v>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002361</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="16" t="str">
         <v>净卖: -845.97万</v>
       </c>
       <c r="E3">
@@ -1895,40 +1895,40 @@
       <c r="H3">
         <v>0.31</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="22">
         <v>9.67</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="23">
         <v>9.05</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="24">
         <v>6.71</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="25">
         <v>5.46</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="17">
         <v>8.89</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="18">
         <v>11.86</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="14">
         <v>6.08</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="26">
         <v>-0.16</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="19">
         <v>0.47</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="15">
         <v>0.62</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="20">
         <v>10.76</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="21">
         <v>192.51</v>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300497</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="34" t="str">
         <v>净卖: -2195.55万</v>
       </c>
       <c r="E4">
@@ -1957,40 +1957,40 @@
       <c r="H4">
         <v>16.67</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="30">
         <v>2.88</v>
       </c>
       <c r="J4" s="35">
         <v>10.88</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="31">
         <v>24.34</v>
       </c>
       <c r="L4" s="32">
         <v>5.76</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="36">
         <v>6.7</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="37">
         <v>7</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="38">
         <v>-8.29</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="39">
         <v>-5.41</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="33">
         <v>-3.59</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="28">
         <v>-7.94</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="27">
         <v>-4.35</v>
       </c>
-      <c r="T4" s="34">
+      <c r="T4" s="29">
         <v>10.76</v>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>603216</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 2090.40万</v>
       </c>
       <c r="E5">
@@ -2022,37 +2022,37 @@
       <c r="I5" s="41">
         <v>0</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="50">
         <v>10</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="42">
         <v>21</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="51">
         <v>13.35</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="52">
         <v>24.64</v>
       </c>
       <c r="N5" s="47">
         <v>37.13</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="40">
         <v>46.41</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="48">
         <v>61.05</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="45">
         <v>44.93</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="43">
         <v>36.41</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="44">
         <v>47.18</v>
       </c>
-      <c r="T5" s="46">
+      <c r="T5" s="49">
         <v>44.98</v>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000949</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="55" t="str">
         <v>净卖: -2847.45万</v>
       </c>
       <c r="E6">
@@ -2081,40 +2081,40 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="58">
         <v>10.03</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="56">
         <v>12.24</v>
       </c>
       <c r="K6" s="65">
         <v>10.62</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="59">
         <v>6.93</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="53">
         <v>3.98</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="60">
         <v>4.87</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="61">
         <v>10.62</v>
       </c>
-      <c r="P6" s="64">
+      <c r="P6" s="57">
         <v>11.5</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="62">
         <v>7.23</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="63">
         <v>-3.54</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="54">
         <v>0</v>
       </c>
-      <c r="T6" s="55">
+      <c r="T6" s="64">
         <v>7.82</v>
       </c>
     </row>
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="70">
+      <c r="I8" s="67">
         <v>80</v>
       </c>
-      <c r="J8" s="71">
+      <c r="J8" s="75">
         <v>100</v>
       </c>
-      <c r="K8" s="74">
+      <c r="K8" s="70">
         <v>100</v>
       </c>
-      <c r="L8" s="75">
+      <c r="L8" s="68">
         <v>100</v>
       </c>
-      <c r="M8" s="67">
+      <c r="M8" s="76">
         <v>100</v>
       </c>
-      <c r="N8" s="76">
+      <c r="N8" s="71">
         <v>100</v>
       </c>
-      <c r="O8" s="77">
+      <c r="O8" s="74">
         <v>80</v>
       </c>
-      <c r="P8" s="66">
+      <c r="P8" s="72">
         <v>60</v>
       </c>
-      <c r="Q8" s="68">
+      <c r="Q8" s="73">
         <v>80</v>
       </c>
-      <c r="R8" s="72">
+      <c r="R8" s="77">
         <v>60</v>
       </c>
       <c r="S8" s="69">
         <v>60</v>
       </c>
-      <c r="T8" s="73">
+      <c r="T8" s="66">
         <v>100</v>
       </c>
     </row>
@@ -2225,40 +2225,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="79">
+      <c r="I9" s="83">
         <v>6.56</v>
       </c>
-      <c r="J9" s="81">
+      <c r="J9" s="88">
         <v>10.12</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="89">
         <v>14.36</v>
       </c>
-      <c r="L9" s="83">
+      <c r="L9" s="84">
         <v>9.2</v>
       </c>
-      <c r="M9" s="84">
+      <c r="M9" s="81">
         <v>14.04</v>
       </c>
-      <c r="N9" s="82">
+      <c r="N9" s="78">
         <v>17.23</v>
       </c>
-      <c r="O9" s="85">
+      <c r="O9" s="79">
         <v>15.48</v>
       </c>
-      <c r="P9" s="88">
+      <c r="P9" s="85">
         <v>17.63</v>
       </c>
-      <c r="Q9" s="89">
+      <c r="Q9" s="80">
         <v>14.83</v>
       </c>
-      <c r="R9" s="80">
+      <c r="R9" s="86">
         <v>10.81</v>
       </c>
-      <c r="S9" s="86">
+      <c r="S9" s="87">
         <v>15.09</v>
       </c>
-      <c r="T9" s="78">
+      <c r="T9" s="82">
         <v>98.42</v>
       </c>
     </row>

--- a/youzi/江东猛龙/index.xlsx
+++ b/youzi/江东猛龙/index.xlsx
@@ -45,13 +45,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB0212E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,12 +57,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB72432"/>
         <bgColor/>
       </patternFill>
@@ -87,31 +75,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,73 +141,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFAE5E7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,37 +237,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F8437"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEA8A93"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,49 +423,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE35E6A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,156 +447,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -495,7 +483,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002361</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -766.84万</v>
       </c>
       <c r="E2">
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="1">
         <v>10.22</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="4">
         <v>8.42</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="2">
         <v>9.14</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="5">
         <v>14.52</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="6">
         <v>25.99</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="8">
         <v>25.27</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="9">
         <v>22.58</v>
       </c>
       <c r="P2" s="11">
         <v>21.15</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="12">
         <v>25.09</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="10">
         <v>28.49</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="7">
         <v>21.86</v>
       </c>
-      <c r="T2" s="12">
-        <v>236.02</v>
+      <c r="T2" s="13">
+        <v>269.71</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002361</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="18" t="str">
         <v>净卖: -845.97万</v>
       </c>
       <c r="E3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>0.31</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="21">
         <v>9.67</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="15">
         <v>9.05</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="16">
         <v>6.71</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="22">
         <v>5.46</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="23">
         <v>8.89</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="24">
         <v>11.86</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="17">
         <v>6.08</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="19">
         <v>-0.16</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="25">
         <v>0.47</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="26">
         <v>0.62</v>
       </c>
       <c r="S3" s="20">
         <v>10.76</v>
       </c>
-      <c r="T3" s="21">
-        <v>192.51</v>
+      <c r="T3" s="14">
+        <v>221.84</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300497</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="31" t="str">
         <v>净卖: -2195.55万</v>
       </c>
       <c r="E4">
@@ -1957,40 +1957,40 @@
       <c r="H4">
         <v>16.67</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="38">
         <v>2.88</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="32">
         <v>10.88</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="29">
         <v>24.34</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="34">
         <v>5.76</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="30">
         <v>6.7</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="35">
         <v>7</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="39">
         <v>-8.29</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="27">
         <v>-5.41</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="36">
         <v>-3.59</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="37">
         <v>-7.94</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="33">
         <v>-4.35</v>
       </c>
-      <c r="T4" s="29">
+      <c r="T4" s="28">
         <v>10.76</v>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>603216</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="52" t="str">
         <v>净买: 2090.40万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>10</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="45">
         <v>0</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="40">
         <v>10</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="46">
         <v>21</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="48">
         <v>13.35</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="44">
         <v>24.64</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="49">
         <v>37.13</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="41">
         <v>46.41</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="47">
         <v>61.05</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="42">
         <v>44.93</v>
       </c>
       <c r="R5" s="43">
         <v>36.41</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="50">
         <v>47.18</v>
       </c>
-      <c r="T5" s="49">
-        <v>44.98</v>
+      <c r="T5" s="51">
+        <v>47.89</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000949</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -2847.45万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="64">
         <v>10.03</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="55">
         <v>12.24</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="56">
         <v>10.62</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="57">
         <v>6.93</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="65">
         <v>3.98</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="58">
         <v>4.87</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="59">
         <v>10.62</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="60">
         <v>11.5</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="53">
         <v>7.23</v>
       </c>
-      <c r="R6" s="63">
+      <c r="R6" s="61">
         <v>-3.54</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="62">
         <v>0</v>
       </c>
-      <c r="T6" s="64">
-        <v>7.82</v>
+      <c r="T6" s="54">
+        <v>18.58</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="67">
+      <c r="I8" s="71">
         <v>80</v>
       </c>
-      <c r="J8" s="75">
+      <c r="J8" s="67">
         <v>100</v>
       </c>
-      <c r="K8" s="70">
+      <c r="K8" s="75">
         <v>100</v>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="76">
         <v>100</v>
       </c>
-      <c r="M8" s="76">
+      <c r="M8" s="73">
         <v>100</v>
       </c>
-      <c r="N8" s="71">
+      <c r="N8" s="72">
         <v>100</v>
       </c>
-      <c r="O8" s="74">
+      <c r="O8" s="77">
         <v>80</v>
       </c>
-      <c r="P8" s="72">
+      <c r="P8" s="68">
         <v>60</v>
       </c>
-      <c r="Q8" s="73">
+      <c r="Q8" s="66">
         <v>80</v>
       </c>
-      <c r="R8" s="77">
+      <c r="R8" s="69">
         <v>60</v>
       </c>
-      <c r="S8" s="69">
+      <c r="S8" s="70">
         <v>60</v>
       </c>
-      <c r="T8" s="66">
+      <c r="T8" s="74">
         <v>100</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="83">
+      <c r="I9" s="80">
         <v>6.56</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="89">
         <v>10.12</v>
       </c>
-      <c r="K9" s="89">
+      <c r="K9" s="81">
         <v>14.36</v>
       </c>
       <c r="L9" s="84">
         <v>9.2</v>
       </c>
-      <c r="M9" s="81">
+      <c r="M9" s="82">
         <v>14.04</v>
       </c>
       <c r="N9" s="78">
         <v>17.23</v>
       </c>
-      <c r="O9" s="79">
+      <c r="O9" s="85">
         <v>15.48</v>
       </c>
-      <c r="P9" s="85">
+      <c r="P9" s="83">
         <v>17.63</v>
       </c>
-      <c r="Q9" s="80">
+      <c r="Q9" s="79">
         <v>14.83</v>
       </c>
-      <c r="R9" s="86">
+      <c r="R9" s="88">
         <v>10.81</v>
       </c>
-      <c r="S9" s="87">
+      <c r="S9" s="86">
         <v>15.09</v>
       </c>
-      <c r="T9" s="82">
-        <v>98.42</v>
+      <c r="T9" s="87">
+        <v>113.76</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/江东猛龙/index.xlsx
+++ b/youzi/江东猛龙/index.xlsx
@@ -39,6 +39,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -51,79 +93,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,7 +189,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,49 +255,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,7 +285,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,79 +375,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,79 +459,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -448,48 +490,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="4">
         <v>10.22</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="1">
         <v>8.42</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="9">
         <v>9.14</v>
       </c>
       <c r="L2" s="5">
         <v>14.52</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="10">
         <v>25.99</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="11">
         <v>25.27</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="2">
         <v>22.58</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="12">
         <v>21.15</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="6">
         <v>25.09</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="7">
         <v>28.49</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="8">
         <v>21.86</v>
       </c>
       <c r="T2" s="13">
-        <v>269.71</v>
+        <v>306.63</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002361</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -845.97万</v>
       </c>
       <c r="E3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>0.31</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="24">
         <v>9.67</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="14">
         <v>9.05</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="25">
         <v>6.71</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="26">
         <v>5.46</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="15">
         <v>8.89</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="18">
         <v>11.86</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="19">
         <v>6.08</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="16">
         <v>-0.16</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="20">
         <v>0.47</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="21">
         <v>0.62</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="22">
         <v>10.76</v>
       </c>
-      <c r="T3" s="14">
-        <v>221.84</v>
+      <c r="T3" s="23">
+        <v>253.98</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300497</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="36" t="str">
         <v>净卖: -2195.55万</v>
       </c>
       <c r="E4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>16.67</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="30">
         <v>2.88</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="31">
         <v>10.88</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="27">
         <v>24.34</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="32">
         <v>5.76</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="37">
         <v>6.7</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="38">
         <v>7</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="33">
         <v>-8.29</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="39">
         <v>-5.41</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="34">
         <v>-3.59</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="28">
         <v>-7.94</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="35">
         <v>-4.35</v>
       </c>
-      <c r="T4" s="28">
-        <v>10.76</v>
+      <c r="T4" s="29">
+        <v>7.29</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>603216</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 2090.40万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>10</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="51">
         <v>0</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="44">
         <v>10</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="45">
         <v>21</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="40">
         <v>13.35</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="52">
         <v>24.64</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="46">
         <v>37.13</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="47">
         <v>46.41</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="41">
         <v>61.05</v>
       </c>
       <c r="Q5" s="42">
         <v>44.93</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="48">
         <v>36.41</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="49">
         <v>47.18</v>
       </c>
-      <c r="T5" s="51">
-        <v>47.89</v>
+      <c r="T5" s="50">
+        <v>47.32</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000949</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="55" t="str">
         <v>净卖: -2847.45万</v>
       </c>
       <c r="E6">
@@ -2081,19 +2081,19 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="61">
         <v>10.03</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="56">
         <v>12.24</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="65">
         <v>10.62</v>
       </c>
       <c r="L6" s="57">
         <v>6.93</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="62">
         <v>3.98</v>
       </c>
       <c r="N6" s="58">
@@ -2102,20 +2102,20 @@
       <c r="O6" s="59">
         <v>10.62</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="63">
         <v>11.5</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="60">
         <v>7.23</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="53">
         <v>-3.54</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="54">
         <v>0</v>
       </c>
-      <c r="T6" s="54">
-        <v>18.58</v>
+      <c r="T6" s="64">
+        <v>18.14</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="71">
+      <c r="I8" s="77">
         <v>80</v>
       </c>
-      <c r="J8" s="67">
+      <c r="J8" s="74">
         <v>100</v>
       </c>
-      <c r="K8" s="75">
+      <c r="K8" s="66">
         <v>100</v>
       </c>
-      <c r="L8" s="76">
+      <c r="L8" s="71">
         <v>100</v>
       </c>
-      <c r="M8" s="73">
+      <c r="M8" s="72">
         <v>100</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="68">
         <v>100</v>
       </c>
-      <c r="O8" s="77">
+      <c r="O8" s="69">
         <v>80</v>
       </c>
-      <c r="P8" s="68">
+      <c r="P8" s="75">
         <v>60</v>
       </c>
-      <c r="Q8" s="66">
+      <c r="Q8" s="73">
         <v>80</v>
       </c>
-      <c r="R8" s="69">
+      <c r="R8" s="70">
         <v>60</v>
       </c>
-      <c r="S8" s="70">
+      <c r="S8" s="76">
         <v>60</v>
       </c>
-      <c r="T8" s="74">
+      <c r="T8" s="67">
         <v>100</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="80">
+      <c r="I9" s="81">
         <v>6.56</v>
       </c>
-      <c r="J9" s="89">
+      <c r="J9" s="82">
         <v>10.12</v>
       </c>
-      <c r="K9" s="81">
+      <c r="K9" s="85">
         <v>14.36</v>
       </c>
-      <c r="L9" s="84">
+      <c r="L9" s="80">
         <v>9.2</v>
       </c>
-      <c r="M9" s="82">
+      <c r="M9" s="86">
         <v>14.04</v>
       </c>
-      <c r="N9" s="78">
+      <c r="N9" s="83">
         <v>17.23</v>
       </c>
-      <c r="O9" s="85">
+      <c r="O9" s="88">
         <v>15.48</v>
       </c>
-      <c r="P9" s="83">
+      <c r="P9" s="89">
         <v>17.63</v>
       </c>
-      <c r="Q9" s="79">
+      <c r="Q9" s="78">
         <v>14.83</v>
       </c>
-      <c r="R9" s="88">
+      <c r="R9" s="87">
         <v>10.81</v>
       </c>
-      <c r="S9" s="86">
+      <c r="S9" s="79">
         <v>15.09</v>
       </c>
-      <c r="T9" s="87">
-        <v>113.76</v>
+      <c r="T9" s="84">
+        <v>126.67</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/江东猛龙/index.xlsx
+++ b/youzi/江东猛龙/index.xlsx
@@ -39,6 +39,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB72432"/>
         <bgColor/>
       </patternFill>
@@ -51,6 +63,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -75,43 +111,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB0212E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,13 +189,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,109 +267,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -255,31 +411,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,144 +459,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -477,19 +483,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002361</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="9" t="str">
         <v>净卖: -766.84万</v>
       </c>
       <c r="E2">
@@ -1833,16 +1833,16 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="8">
         <v>10.22</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="3">
         <v>8.42</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="13">
         <v>9.14</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="4">
         <v>14.52</v>
       </c>
       <c r="M2" s="10">
@@ -1851,23 +1851,23 @@
       <c r="N2" s="11">
         <v>25.27</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="5">
         <v>22.58</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="6">
         <v>21.15</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="12">
         <v>25.09</v>
       </c>
       <c r="R2" s="7">
         <v>28.49</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="1">
         <v>21.86</v>
       </c>
-      <c r="T2" s="13">
-        <v>306.63</v>
+      <c r="T2" s="2">
+        <v>284.59</v>
       </c>
     </row>
     <row r="3">
@@ -1898,38 +1898,38 @@
       <c r="I3" s="24">
         <v>9.67</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="25">
         <v>9.05</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="18">
         <v>6.71</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="19">
         <v>5.46</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="20">
         <v>8.89</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="26">
         <v>11.86</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="14">
         <v>6.08</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="21">
         <v>-0.16</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="15">
         <v>0.47</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="22">
         <v>0.62</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="23">
         <v>10.76</v>
       </c>
-      <c r="T3" s="23">
-        <v>253.98</v>
+      <c r="T3" s="16">
+        <v>234.79</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300497</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -2195.55万</v>
       </c>
       <c r="E4">
@@ -1960,38 +1960,38 @@
       <c r="I4" s="30">
         <v>2.88</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="37">
         <v>10.88</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="31">
         <v>24.34</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="35">
         <v>5.76</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="32">
         <v>6.7</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="39">
         <v>7</v>
       </c>
       <c r="O4" s="33">
         <v>-8.29</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="34">
         <v>-5.41</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="27">
         <v>-3.59</v>
       </c>
       <c r="R4" s="28">
         <v>-7.94</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="36">
         <v>-4.35</v>
       </c>
       <c r="T4" s="29">
-        <v>7.29</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>603216</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="50" t="str">
         <v>净买: 2090.40万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>10</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="43">
         <v>0</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="51">
         <v>10</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="40">
         <v>21</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="44">
         <v>13.35</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="46">
         <v>24.64</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="41">
         <v>37.13</v>
       </c>
       <c r="O5" s="47">
         <v>46.41</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="45">
         <v>61.05</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="48">
         <v>44.93</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="49">
         <v>36.41</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="42">
         <v>47.18</v>
       </c>
-      <c r="T5" s="50">
-        <v>47.32</v>
+      <c r="T5" s="52">
+        <v>40.77</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000949</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="62" t="str">
         <v>净卖: -2847.45万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="63">
         <v>10.03</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="59">
         <v>12.24</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="60">
         <v>10.62</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="55">
         <v>6.93</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="64">
         <v>3.98</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="65">
         <v>4.87</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="56">
         <v>10.62</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="53">
         <v>11.5</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="61">
         <v>7.23</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="57">
         <v>-3.54</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="58">
         <v>0</v>
       </c>
-      <c r="T6" s="64">
-        <v>18.14</v>
+      <c r="T6" s="54">
+        <v>16.22</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="77">
+      <c r="I8" s="69">
         <v>80</v>
       </c>
-      <c r="J8" s="74">
+      <c r="J8" s="68">
         <v>100</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="70">
         <v>100</v>
       </c>
-      <c r="L8" s="71">
+      <c r="L8" s="72">
         <v>100</v>
       </c>
-      <c r="M8" s="72">
+      <c r="M8" s="77">
         <v>100</v>
       </c>
-      <c r="N8" s="68">
+      <c r="N8" s="66">
         <v>100</v>
       </c>
-      <c r="O8" s="69">
+      <c r="O8" s="73">
         <v>80</v>
       </c>
-      <c r="P8" s="75">
+      <c r="P8" s="71">
         <v>60</v>
       </c>
-      <c r="Q8" s="73">
+      <c r="Q8" s="74">
         <v>80</v>
       </c>
-      <c r="R8" s="70">
+      <c r="R8" s="67">
         <v>60</v>
       </c>
-      <c r="S8" s="76">
+      <c r="S8" s="75">
         <v>60</v>
       </c>
-      <c r="T8" s="67">
+      <c r="T8" s="76">
         <v>100</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="81">
+      <c r="I9" s="89">
         <v>6.56</v>
       </c>
-      <c r="J9" s="82">
+      <c r="J9" s="78">
         <v>10.12</v>
       </c>
-      <c r="K9" s="85">
+      <c r="K9" s="79">
         <v>14.36</v>
       </c>
       <c r="L9" s="80">
         <v>9.2</v>
       </c>
-      <c r="M9" s="86">
+      <c r="M9" s="85">
         <v>14.04</v>
       </c>
-      <c r="N9" s="83">
+      <c r="N9" s="81">
         <v>17.23</v>
       </c>
-      <c r="O9" s="88">
+      <c r="O9" s="82">
         <v>15.48</v>
       </c>
-      <c r="P9" s="89">
+      <c r="P9" s="83">
         <v>17.63</v>
       </c>
-      <c r="Q9" s="78">
+      <c r="Q9" s="86">
         <v>14.83</v>
       </c>
       <c r="R9" s="87">
         <v>10.81</v>
       </c>
-      <c r="S9" s="79">
+      <c r="S9" s="88">
         <v>15.09</v>
       </c>
       <c r="T9" s="84">
-        <v>126.67</v>
+        <v>116.78</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/江东猛龙/index.xlsx
+++ b/youzi/江东猛龙/index.xlsx
@@ -39,7 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,19 +117,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,97 +195,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC92C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,37 +249,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1F8437"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC12837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,19 +273,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,61 +399,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,90 +453,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -453,12 +471,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -472,18 +484,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002361</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="10" t="str">
         <v>净卖: -766.84万</v>
       </c>
       <c r="E2">
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="11">
         <v>10.22</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="12">
         <v>8.42</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="1">
         <v>9.14</v>
       </c>
       <c r="L2" s="4">
         <v>14.52</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="13">
         <v>25.99</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="2">
         <v>25.27</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="8">
         <v>22.58</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="5">
         <v>21.15</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="9">
         <v>25.09</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="6">
         <v>28.49</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="7">
         <v>21.86</v>
       </c>
-      <c r="T2" s="2">
-        <v>284.59</v>
+      <c r="T2" s="3">
+        <v>288.17</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002361</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="26" t="str">
         <v>净卖: -845.97万</v>
       </c>
       <c r="E3">
@@ -1895,41 +1895,41 @@
       <c r="H3">
         <v>0.31</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="22">
         <v>9.67</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="14">
         <v>9.05</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="20">
         <v>6.71</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="15">
         <v>5.46</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="21">
         <v>8.89</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="23">
         <v>11.86</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="16">
         <v>6.08</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="24">
         <v>-0.16</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="17">
         <v>0.47</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="18">
         <v>0.62</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="19">
         <v>10.76</v>
       </c>
-      <c r="T3" s="16">
-        <v>234.79</v>
+      <c r="T3" s="25">
+        <v>237.91</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300497</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -2195.55万</v>
       </c>
       <c r="E4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>16.67</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="33">
         <v>2.88</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="28">
         <v>10.88</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="34">
         <v>24.34</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="29">
         <v>5.76</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="30">
         <v>6.7</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="31">
         <v>7</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="36">
         <v>-8.29</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="39">
         <v>-5.41</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="35">
         <v>-3.59</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="37">
         <v>-7.94</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="32">
         <v>-4.35</v>
       </c>
-      <c r="T4" s="29">
-        <v>7.52</v>
+      <c r="T4" s="38">
+        <v>16.05</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>603216</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="40" t="str">
         <v>净买: 2090.40万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>10</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="41">
         <v>0</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="50">
         <v>10</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="44">
         <v>21</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="51">
         <v>13.35</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="45">
         <v>24.64</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="47">
         <v>37.13</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="48">
         <v>46.41</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="49">
         <v>61.05</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="52">
         <v>44.93</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="42">
         <v>36.41</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="43">
         <v>47.18</v>
       </c>
-      <c r="T5" s="52">
-        <v>40.77</v>
+      <c r="T5" s="46">
+        <v>43.49</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000949</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -2847.45万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="58">
         <v>10.03</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="55">
         <v>12.24</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="61">
         <v>10.62</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="62">
         <v>6.93</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="63">
         <v>3.98</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="64">
         <v>4.87</v>
       </c>
       <c r="O6" s="56">
         <v>10.62</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="57">
         <v>11.5</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="65">
         <v>7.23</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="53">
         <v>-3.54</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="59">
         <v>0</v>
       </c>
       <c r="T6" s="54">
-        <v>16.22</v>
+        <v>15.04</v>
       </c>
     </row>
     <row r="7">
@@ -2177,40 +2177,40 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="69">
+      <c r="I8" s="74">
         <v>80</v>
       </c>
-      <c r="J8" s="68">
+      <c r="J8" s="75">
         <v>100</v>
       </c>
-      <c r="K8" s="70">
+      <c r="K8" s="66">
         <v>100</v>
       </c>
-      <c r="L8" s="72">
+      <c r="L8" s="76">
         <v>100</v>
       </c>
-      <c r="M8" s="77">
+      <c r="M8" s="68">
         <v>100</v>
       </c>
-      <c r="N8" s="66">
+      <c r="N8" s="69">
         <v>100</v>
       </c>
-      <c r="O8" s="73">
+      <c r="O8" s="72">
         <v>80</v>
       </c>
-      <c r="P8" s="71">
+      <c r="P8" s="67">
         <v>60</v>
       </c>
-      <c r="Q8" s="74">
+      <c r="Q8" s="77">
         <v>80</v>
       </c>
-      <c r="R8" s="67">
+      <c r="R8" s="73">
         <v>60</v>
       </c>
-      <c r="S8" s="75">
+      <c r="S8" s="70">
         <v>60</v>
       </c>
-      <c r="T8" s="76">
+      <c r="T8" s="71">
         <v>100</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="89">
+      <c r="I9" s="78">
         <v>6.56</v>
       </c>
-      <c r="J9" s="78">
+      <c r="J9" s="83">
         <v>10.12</v>
       </c>
       <c r="K9" s="79">
         <v>14.36</v>
       </c>
-      <c r="L9" s="80">
+      <c r="L9" s="87">
         <v>9.2</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="80">
         <v>14.04</v>
       </c>
-      <c r="N9" s="81">
+      <c r="N9" s="88">
         <v>17.23</v>
       </c>
-      <c r="O9" s="82">
+      <c r="O9" s="84">
         <v>15.48</v>
       </c>
-      <c r="P9" s="83">
+      <c r="P9" s="85">
         <v>17.63</v>
       </c>
-      <c r="Q9" s="86">
+      <c r="Q9" s="82">
         <v>14.83</v>
       </c>
-      <c r="R9" s="87">
+      <c r="R9" s="89">
         <v>10.81</v>
       </c>
-      <c r="S9" s="88">
+      <c r="S9" s="81">
         <v>15.09</v>
       </c>
-      <c r="T9" s="84">
-        <v>116.78</v>
+      <c r="T9" s="86">
+        <v>120.13</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/江东猛龙/index.xlsx
+++ b/youzi/江东猛龙/index.xlsx
@@ -39,6 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB0212E"/>
         <bgColor/>
       </patternFill>
@@ -75,24 +81,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -117,6 +105,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB1212F"/>
         <bgColor/>
       </patternFill>
@@ -129,6 +129,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD02F3F"/>
         <bgColor/>
       </patternFill>
@@ -141,13 +195,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF43B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,25 +243,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,6 +273,150 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3A49"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -207,67 +429,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF43B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,162 +447,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3A49"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -442,18 +454,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1818,7 +1818,7 @@
       <c r="C2" t="str">
         <v>002361</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="8" t="str">
         <v>净卖: -766.84万</v>
       </c>
       <c r="E2">
@@ -1833,41 +1833,41 @@
       <c r="H2">
         <v>-0.18</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="1">
         <v>10.22</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="10">
         <v>8.42</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="2">
         <v>9.14</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="11">
         <v>14.52</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="3">
         <v>25.99</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="9">
         <v>25.27</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="4">
         <v>22.58</v>
       </c>
       <c r="P2" s="5">
         <v>21.15</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="12">
         <v>25.09</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="13">
         <v>28.49</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="6">
         <v>21.86</v>
       </c>
-      <c r="T2" s="3">
-        <v>288.17</v>
+      <c r="T2" s="7">
+        <v>258.78</v>
       </c>
     </row>
     <row r="3">
@@ -1880,7 +1880,7 @@
       <c r="C3" t="str">
         <v>002361</v>
       </c>
-      <c r="D3" s="26" t="str">
+      <c r="D3" s="19" t="str">
         <v>净卖: -845.97万</v>
       </c>
       <c r="E3">
@@ -1895,13 +1895,13 @@
       <c r="H3">
         <v>0.31</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="20">
         <v>9.67</v>
       </c>
       <c r="J3" s="14">
         <v>9.05</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="24">
         <v>6.71</v>
       </c>
       <c r="L3" s="15">
@@ -1910,26 +1910,26 @@
       <c r="M3" s="21">
         <v>8.89</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="22">
         <v>11.86</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="25">
         <v>6.08</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="18">
         <v>-0.16</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="26">
         <v>0.47</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="16">
         <v>0.62</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="23">
         <v>10.76</v>
       </c>
-      <c r="T3" s="25">
-        <v>237.91</v>
+      <c r="T3" s="17">
+        <v>212.32</v>
       </c>
     </row>
     <row r="4">
@@ -1942,7 +1942,7 @@
       <c r="C4" t="str">
         <v>300497</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="39" t="str">
         <v>净卖: -2195.55万</v>
       </c>
       <c r="E4">
@@ -1957,41 +1957,41 @@
       <c r="H4">
         <v>16.67</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="32">
         <v>2.88</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="35">
         <v>10.88</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="29">
         <v>24.34</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="33">
         <v>5.76</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="34">
         <v>6.7</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="36">
         <v>7</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="37">
         <v>-8.29</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="27">
         <v>-5.41</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="30">
         <v>-3.59</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="31">
         <v>-7.94</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="28">
         <v>-4.35</v>
       </c>
       <c r="T4" s="38">
-        <v>16.05</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="5">
@@ -2004,7 +2004,7 @@
       <c r="C5" t="str">
         <v>603216</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 2090.40万</v>
       </c>
       <c r="E5">
@@ -2019,41 +2019,41 @@
       <c r="H5">
         <v>10</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="40">
         <v>0</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="41">
         <v>10</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="48">
         <v>21</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="44">
         <v>13.35</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="49">
         <v>24.64</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="42">
         <v>37.13</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="45">
         <v>46.41</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="50">
         <v>61.05</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="51">
         <v>44.93</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="46">
         <v>36.41</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="52">
         <v>47.18</v>
       </c>
-      <c r="T5" s="46">
-        <v>43.49</v>
+      <c r="T5" s="47">
+        <v>40.91</v>
       </c>
     </row>
     <row r="6">
@@ -2066,7 +2066,7 @@
       <c r="C6" t="str">
         <v>000949</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="64" t="str">
         <v>净卖: -2847.45万</v>
       </c>
       <c r="E6">
@@ -2081,41 +2081,41 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="65">
         <v>10.03</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="59">
         <v>12.24</v>
       </c>
       <c r="K6" s="61">
         <v>10.62</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="53">
         <v>6.93</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="54">
         <v>3.98</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="62">
         <v>4.87</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="55">
         <v>10.62</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="56">
         <v>11.5</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="57">
         <v>7.23</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="63">
         <v>-3.54</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="60">
         <v>0</v>
       </c>
-      <c r="T6" s="54">
-        <v>15.04</v>
+      <c r="T6" s="58">
+        <v>14.9</v>
       </c>
     </row>
     <row r="7">
@@ -2177,28 +2177,28 @@
       <c r="F8" t="str"/>
       <c r="G8" t="str"/>
       <c r="H8" t="str"/>
-      <c r="I8" s="74">
+      <c r="I8" s="66">
         <v>80</v>
       </c>
-      <c r="J8" s="75">
+      <c r="J8" s="74">
         <v>100</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="71">
         <v>100</v>
       </c>
-      <c r="L8" s="76">
+      <c r="L8" s="67">
         <v>100</v>
       </c>
-      <c r="M8" s="68">
+      <c r="M8" s="72">
         <v>100</v>
       </c>
-      <c r="N8" s="69">
+      <c r="N8" s="75">
         <v>100</v>
       </c>
-      <c r="O8" s="72">
+      <c r="O8" s="76">
         <v>80</v>
       </c>
-      <c r="P8" s="67">
+      <c r="P8" s="68">
         <v>60</v>
       </c>
       <c r="Q8" s="77">
@@ -2207,10 +2207,10 @@
       <c r="R8" s="73">
         <v>60</v>
       </c>
-      <c r="S8" s="70">
+      <c r="S8" s="69">
         <v>60</v>
       </c>
-      <c r="T8" s="71">
+      <c r="T8" s="70">
         <v>100</v>
       </c>
     </row>
@@ -2225,41 +2225,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="78">
+      <c r="I9" s="80">
         <v>6.56</v>
       </c>
-      <c r="J9" s="83">
+      <c r="J9" s="81">
         <v>10.12</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="85">
         <v>14.36</v>
       </c>
-      <c r="L9" s="87">
+      <c r="L9" s="82">
         <v>9.2</v>
       </c>
-      <c r="M9" s="80">
+      <c r="M9" s="89">
         <v>14.04</v>
       </c>
-      <c r="N9" s="88">
+      <c r="N9" s="83">
         <v>17.23</v>
       </c>
-      <c r="O9" s="84">
+      <c r="O9" s="78">
         <v>15.48</v>
       </c>
-      <c r="P9" s="85">
+      <c r="P9" s="84">
         <v>17.63</v>
       </c>
-      <c r="Q9" s="82">
+      <c r="Q9" s="79">
         <v>14.83</v>
       </c>
-      <c r="R9" s="89">
+      <c r="R9" s="86">
         <v>10.81</v>
       </c>
-      <c r="S9" s="81">
+      <c r="S9" s="87">
         <v>15.09</v>
       </c>
-      <c r="T9" s="86">
-        <v>120.13</v>
+      <c r="T9" s="88">
+        <v>107.96</v>
       </c>
     </row>
   </sheetData>
